--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129117636</v>
       </c>
       <c r="B4" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129117613</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000448</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000447</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129117636</v>
+        <v>129117613</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129117613</v>
+        <v>129117636</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
         <v>129118126</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48823-2025 artfynd.xlsx
+++ b/artfynd/A 48823-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,8 +1200,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>